--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-mcu-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-mcu-easy.xlsx
@@ -460,19 +460,19 @@
         <v>UART là giao thức bất đồng bộ (Asynchronous), truyền nhận full-duplex qua 2 đường độc lập Tx và Rx (cần nối chung chân GND làm mốc điện áp).</v>
       </c>
       <c r="F2" t="str">
+        <v>4 dây tín hiệu: MISO, MOSI, SCK, và SS — phục vụ truyền nhận dữ liệu đồng bộ</v>
+      </c>
+      <c r="G2" t="str">
+        <v>1 dây tín hiệu duy nhất dùng chung cho cả truyền và nhận dữ liệu đồng thời</v>
+      </c>
+      <c r="H2" t="str">
         <v>2 dây tín hiệu: Tx (Truyền) và Rx (Nhận) — kết nối chéo giữa hai thiết bị (Tx thiết bị A nối Rx thiết bị B)</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>3 dây tín hiệu: SCL (Xung nhịp), SDA (Dữ liệu), và GND (Đất)</v>
       </c>
-      <c r="H2" t="str">
-        <v>4 dây tín hiệu: MISO, MOSI, SCK, và SS — phục vụ truyền nhận dữ liệu đồng bộ</v>
-      </c>
-      <c r="I2" t="str">
-        <v>1 dây tín hiệu duy nhất dùng chung cho cả truyền và nhận dữ liệu đồng thời</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Do không có đường truyền xung nhịp (Clock) để đồng bộ cứng, UART sử dụng Baudrate thiết lập sẵn và các bit Start/Stop trong khung truyền để đồng bộ luồng nhận.</v>
       </c>
       <c r="F3" t="str">
+        <v>Vì nó chỉ cho phép truyền dữ liệu theo một chiều duy nhất tại một thời điểm</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Vì tín hiệu truyền đi không cần tuân theo bất kỳ định dạng khung truyền nào</v>
+      </c>
+      <c r="H3" t="str">
         <v>Vì nó không sử dụng dây dẫn tín hiệu xung nhịp (Clock) chung giữa hai thiết bị; hai bên tự thống nhất tốc độ truyền (Baud rate)</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>Vì tốc độ truyền dữ liệu của nó thay đổi liên tục một cách ngẫu nhiên khi chạy</v>
       </c>
-      <c r="H3" t="str">
-        <v>Vì nó chỉ cho phép truyền dữ liệu theo một chiều duy nhất tại một thời điểm</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Vì tín hiệu truyền đi không cần tuân theo bất kỳ định dạng khung truyền nào</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>I2C là giao thức đồng bộ (Synchronous), half-duplex, sử dụng đường dữ liệu SDA và đường xung nhịp SCL để điều phối việc truyền tin.</v>
       </c>
       <c r="F4" t="str">
-        <v>SDA (Serial Data) dùng để truyền nhận dữ liệu; SCL (Serial Clock) dùng để truyền tín hiệu xung nhịp đồng bộ</v>
+        <v>SDA dùng để truyền tín hiệu bắt đầu; SCL dùng để truyền tín hiệu kết thúc giao tiếp</v>
       </c>
       <c r="G4" t="str">
         <v>SDA dùng để cấp nguồn điện; SCL dùng để nối đất cho mạch ngoại vi</v>
       </c>
       <c r="H4" t="str">
-        <v>SDA dùng để truyền tín hiệu bắt đầu; SCL dùng để truyền tín hiệu kết thúc giao tiếp</v>
+        <v>Cả hai dây SDA và SCL đều thực hiện truyền nhận dữ liệu song song để tăng tốc độ</v>
       </c>
       <c r="I4" t="str">
-        <v>Cả hai dây SDA và SCL đều thực hiện truyền nhận dữ liệu song song để tăng tốc độ</v>
+        <v>SDA (Serial Data) dùng để truyền nhận dữ liệu; SCL (Serial Clock) dùng để truyền tín hiệu xung nhịp đồng bộ</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         <v>SCK (Serial Clock) — dùng để phát xung nhịp đồng bộ từ Master</v>
       </c>
       <c r="H5" t="str">
+        <v>MISO (Master In Slave Out) — dùng để nhận dữ liệu từ Slave về Master</v>
+      </c>
+      <c r="I5" t="str">
         <v>MOSI (Master Out Slave In) — dùng để truyền dữ liệu từ Master đến Slave</v>
-      </c>
-      <c r="I5" t="str">
-        <v>MISO (Master In Slave Out) — dùng để nhận dữ liệu từ Slave về Master</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Chân GPIO để trống ở chế độ Input sẽ bị nhiễu môi trường làm thay đổi logic liên tục (floating). Pull-up kéo chân lên mức VCC để đảm bảo trạng thái logic ổn định.</v>
       </c>
       <c r="F6" t="str">
-        <v>Giữ chân GPIO luôn ở mức điện áp cao (Logic 1) khi không có tín hiệu bên ngoài tác động, tránh trạng thái lơ lửng (Floating)</v>
+        <v>Tự động chuyển đổi chân GPIO từ chế độ đầu vào sang chế độ đầu ra</v>
       </c>
       <c r="G6" t="str">
         <v>Tăng dòng điện đầu ra tối đa của chân GPIO để thắp sáng các bóng đèn công suất lớn</v>
       </c>
       <c r="H6" t="str">
+        <v>Giữ chân GPIO luôn ở mức điện áp cao (Logic 1) khi không có tín hiệu bên ngoài tác động, tránh trạng thái lơ lửng (Floating)</v>
+      </c>
+      <c r="I6" t="str">
         <v>Bảo vệ vi điều khiển chống lại các hiện tượng quá áp hoặc sét đánh vào mạch</v>
       </c>
-      <c r="I6" t="str">
-        <v>Tự động chuyển đổi chân GPIO từ chế độ đầu vào sang chế độ đầu ra</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         <v>Chuyển đổi tín hiệu điện áp liên tục (Analog) bên ngoài thành giá trị số (Digital) để CPU xử lý</v>
       </c>
       <c r="G7" t="str">
+        <v>Chuyển đổi dòng điện xoay chiều (AC) thành dòng điện một chiều (DC) cấp nguồn cho mạch</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Tăng tần số xung nhịp hoạt động của nhân vi điều khiển lên tối đa</v>
+      </c>
+      <c r="I7" t="str">
         <v>Chuyển đổi các câu lệnh lập trình C thành mã máy nhị phân nạp vào Flash</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Chuyển đổi dòng điện xoay chiều (AC) thành dòng điện một chiều (DC) cấp nguồn cho mạch</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Tăng tần số xung nhịp hoạt động của nhân vi điều khiển lên tối đa</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -655,10 +655,10 @@
         <v>Cho phép truyền dữ liệu trực tiếp giữa bộ nhớ và ngoại vi (hoặc bộ nhớ - bộ nhớ) mà không cần sự can thiệp của CPU, giúp giải phóng tài nguyên CPU</v>
       </c>
       <c r="G8" t="str">
+        <v>Cho phép vi điều khiển kết nối trực tiếp vào mạng internet không dây Wi-Fi</v>
+      </c>
+      <c r="H8" t="str">
         <v>Tự động tối ưu hóa cấu trúc của các bảng cơ sở dữ liệu quan hệ lưu trữ trên vi điều khiển</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Cho phép vi điều khiển kết nối trực tiếp vào mạng internet không dây Wi-Fi</v>
       </c>
       <c r="I8" t="str">
         <v>Tự động tăng gấp đôi dung lượng bộ nhớ RAM vật lý của hệ thống vi điều khiển</v>
@@ -684,19 +684,19 @@
         <v>SPI sử dụng 2 đường dữ liệu riêng biệt MOSI và MISO hoạt động đồng bộ theo nhịp SCK, cho phép gửi và nhận dữ liệu đồng thời ở tốc độ rất cao.</v>
       </c>
       <c r="F9" t="str">
-        <v>Full-duplex (Song công) — cho phép truyền và nhận dữ liệu đồng thời trên hai đường MOSI và MISO độc lập</v>
+        <v>Simplex (Đơn công) — chỉ cho phép truyền dữ liệu một chiều cố định từ Master đến Slave</v>
       </c>
       <c r="G9" t="str">
         <v>Half-duplex (Bán song công) — chỉ cho phép truyền hoặc nhận tại một thời điểm trên một dây dẫn</v>
       </c>
       <c r="H9" t="str">
-        <v>Simplex (Đơn công) — chỉ cho phép truyền dữ liệu một chiều cố định từ Master đến Slave</v>
+        <v>Asynchronous (Bất đồng bộ) — truyền dữ liệu không cần đồng bộ xung nhịp</v>
       </c>
       <c r="I9" t="str">
-        <v>Asynchronous (Bất đồng bộ) — truyền dữ liệu không cần đồng bộ xung nhịp</v>
+        <v>Full-duplex (Song công) — cho phép truyền và nhận dữ liệu đồng thời trên hai đường MOSI và MISO độc lập</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Kích hoạt chân RESET (thường kéo xuống mức thấp) sẽ khởi động lại phần cứng của MCU, nạp lại thanh ghi PC (Program Counter) về địa chỉ vector khởi động.</v>
       </c>
       <c r="F10" t="str">
+        <v>Tăng điện áp cấp cho các chân GPIO đầu ra lên mức an toàn</v>
+      </c>
+      <c r="G10" t="str">
         <v>Đưa vi điều khiển về trạng thái ban đầu, khởi động lại chương trình và thiết lập lại các thanh ghi ngoại vi về giá trị mặc định</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Xóa sạch vĩnh viễn toàn bộ mã nguồn chương trình đã nạp trong bộ nhớ Flash</v>
       </c>
       <c r="H10" t="str">
         <v>Chuyển vi điều khiển sang chế độ tiết kiệm năng lượng tối đa (Deep Sleep)</v>
       </c>
       <c r="I10" t="str">
-        <v>Tăng điện áp cấp cho các chân GPIO đầu ra lên mức an toàn</v>
+        <v>Xóa sạch vĩnh viễn toàn bộ mã nguồn chương trình đã nạp trong bộ nhớ Flash</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Độ phân giải càng cao thì phép đo điện áp càng mịn. Ví dụ ADC 12-bit đo dải 0-3.3V sẽ có độ nhạy tối thiểu là 3.3V / 4096 ≈ 0.8 mV.</v>
       </c>
       <c r="F11" t="str">
+        <v>Tốc độ chuyển đổi dữ liệu tối đa tính bằng số mẫu trên một giây (SPS)</v>
+      </c>
+      <c r="G11" t="str">
         <v>Số lượng các mức lượng tử hóa mà ADC có thể biểu diễn; 12-bit tương đương với 2^12 = 4096 mức giá trị số</v>
       </c>
-      <c r="G11" t="str">
-        <v>Tốc độ chuyển đổi dữ liệu tối đa tính bằng số mẫu trên một giây (SPS)</v>
-      </c>
       <c r="H11" t="str">
+        <v>Độ chính xác về mặt thời gian của bộ hẹn giờ (Timer) dùng để kích hoạt ADC</v>
+      </c>
+      <c r="I11" t="str">
         <v>Số lượng chân đầu vào Analog tối đa mà bộ ADC đó có thể đọc đồng thời</v>
       </c>
-      <c r="I11" t="str">
-        <v>Độ chính xác về mặt thời gian của bộ hẹn giờ (Timer) dùng để kích hoạt ADC</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
